--- a/output/CVE_20260901.xlsx
+++ b/output/CVE_20260901.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -547,12 +547,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>n8n GmbH</t>
+          <t>n8n</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>&lt;2.31.5|&lt;2.32.1</t>
+          <t>&gt;=2.31.0,&lt;2.31.5|==2.32.0</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -562,17 +562,17 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>9.9</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>CVSS:4.0/AV:N/AC:L/AT:N/PR:L/UI:N/VC:H/VI:H/VA:H/SC:N/SI:N/SA:N/E:X/CR:X/IR:X/AR:X/MAV:X/MAC:X/MAT:X/MPR:X/MUI:X/MVC:X/MVI:X/MVA:X/MSC:X/MSI:X/MSA:X/S:X/AU:X/R:X/V:X/RE:X/U:X</t>
+          <t>CVSS:3.1/AV:N/AC:L/PR:L/UI:N/S:C/C:H/I:H/A:H</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -612,24 +612,24 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>20260901001242</t>
+          <t>20260901225433</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>CVE-2026-43629</t>
+          <t>CVE-2026-37007</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>llama.cpp</t>
+          <t>CrewAI</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>ggml.ai</t>
+          <t>CrewAI</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -640,27 +640,27 @@
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>CVSS:3.1/AV:N/AC:H/PR:N/UI:N/S:U/C:H/I:H/A:H</t>
+          <t>CVSS:3.1/AV:N/AC:L/PR:N/UI:N/S:U/C:H/I:H/A:H</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>20260806</t>
+          <t>20260827</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -670,12 +670,12 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>[버전범위 불명확] llama.cpp builds b4882 through b9058 contain a heap buffer overflow vulnerability in the KV cache state restore path where the state_read_data() function computes write size without overflow checking, allowing attackers with write access to the slot_save_path directory to corrupt heap memory. Attackers can craft malicious state files where cell_count multiplication overflows or exceeds tensor buffer allocation to write attacker-controlled bytes past buffer boundaries, potentially resulting in heap metadata corruption, model weight corruption, or arbitrary code execution via function pointer overwrite.</t>
+          <t>[버전범위 불명확] A vulnerability in FileWriterTool in crewai-tools &lt;= 1.10.2rc1 allows a remote attacker to achieve code execution via malicious path traversal sequences in the filename argument.</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/Vladimir-tokarev-cyera/llama-cpp-security-patches</t>
+          <t>https://github.com/crewAIInc/crewAI/commit/713fa7d</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -685,60 +685,60 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>pypi</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>20260901001242</t>
+          <t>20260901225433</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>CVE-2026-43631</t>
+          <t>CVE-2026-77070</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>llama.cpp</t>
+          <t>n8n</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>ggml.ai</t>
+          <t>n8n</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>&lt;1.123.69|&gt;=2.33.0,&lt;2.33.4|==2.34.0</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>CVSS:3.1/AV:N/AC:H/PR:N/UI:N/S:U/C:H/I:H/A:H</t>
+          <t>CVSS:3.1/AV:N/AC:L/PR:N/UI:N/S:U/C:H/I:H/A:H</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20260806</t>
+          <t>20260820</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>[버전범위 불명확] llama.cpp builds b7492 through the latest b9060 contains a use-after-free vulnerability in the vocab pointer of llama-server when the --sleep-idle-seconds feature is enabled, allowing unauthenticated remote attackers to execute arbitrary code. Attackers can trigger the vulnerability by sending requests to affected endpoints while the server transitions to sleep mode, causing concurrent worker threads to dereference a freed vocab pointer that can be reclaimed with attacker-controlled data to achieve remote code execution.</t>
+          <t>1.123.69, 2.33.4 및 2.34.1 이전의 n8n에는 MongoDB 연산자를 삭제하지 않고 표현식 확인 후 Query 매개변수를 JSON으로 구문 분석하는 MongoDB 노드의 찾기, 삭제 및 집계 작업에 NoSQL 주입 취약점이 포함되어 있습니다. 해결된 쿼리(예: 외부 제어 데이터를 통해)에 영향을 미칠 수 있는 공격자는 $ne 또는 $where와 같은 연산자를 주입하여 의도된 단일 문서 조회를 전체 컬렉션 공개, 전체 컬렉션 삭제 또는 데이터베이스 서버의 기타 작업으로 전환할 수 있습니다.</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/Vladimir-tokarev-cyera/llama-cpp-security-patches</t>
+          <t>https://github.com/n8n-io/n8n/security/advisories/GHSA-953p-jm2c-8h5j</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -763,60 +763,60 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>npm</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20260901001242</t>
+          <t>20260901225433</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>CVE-2026-43632</t>
+          <t>CVE-2026-77071</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>llama.cpp</t>
+          <t>n8n</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>ggml.ai</t>
+          <t>n8n</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>&lt;1.123.69|&gt;=2.33.0,&lt;2.33.4|==2.34.0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>CVSS:3.1/AV:N/AC:H/PR:N/UI:N/S:U/C:H/I:H/A:H</t>
+          <t>CVSS:3.1/AV:N/AC:L/PR:N/UI:N/S:U/C:H/I:H/A:H</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20260806</t>
+          <t>20260820</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -826,12 +826,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>[버전범위 불명확] llama.cpp builds b7492 through the latest b9060 contains a use-after-free vulnerability in llama-server affecting six tokenization endpoints (/tokenize, /detokenize, /infill, /apply-template, /rerank, and /anthropic/count_tokens) that bypass the task queue and access ctx_server.vocab directly on HTTP worker threads. Attackers can exploit a time-of-check-time-of-use race condition where the main thread destroys and frees vocab after the synchronization lock is released but before the handler finishes using it, causing a crash or potential code execution when --sleep-idle-seconds is configured.</t>
+          <t>1.123.69, 2.33.4 및 2.34.1 이전의 n8n에는 Supabase 노드의 Row Get Many, 삭제 및 업데이트 작업에 PostgREST 필터 주입 취약점이 포함되어 있습니다. 이 취약점은 이스케이프 없이 표현식 바인딩 가능한 값을 연결하여 필터 쿼리를 작성했습니다. 공격자는 모든 행과 일치하도록 필터를 확대하는 조건을 주입하여 의도한 단일 행 작업을 전체 테이블 공개, 삭제 또는 수정으로 전환할 수 있습니다.</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/Vladimir-tokarev-cyera/llama-cpp-security-patches</t>
+          <t>https://github.com/n8n-io/n8n/security/advisories/GHSA-f4f3-2g67-4vhm</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -841,34 +841,34 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>npm</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20260901001242</t>
+          <t>20260901225433</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>CVE-2026-43622</t>
+          <t>CVE-2026-72642</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>llama.cpp</t>
+          <t>Elasticsearch</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>ggml.ai</t>
+          <t>elastic</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>&gt;=8.19.0,&lt;8.19.20|&gt;=9.4.0,&lt;9.4.5|&gt;=9.5.0,&lt;9.5.1</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -879,22 +879,22 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>CVSS:3.1/AV:L/AC:L/PR:N/UI:R/S:U/C:H/I:H/A:H</t>
+          <t>CVSS:3.1/AV:N/AC:L/PR:L/UI:N/S:U/C:H/I:H/A:H</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20260806</t>
+          <t>20260813</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -904,12 +904,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>[버전범위 불명확] llama.cpp builds b1886 through b7445 contain a double free vulnerability in the LLaMA-Android JNI wrapper where new_1batch() allocates memory using malloc() while free_1batch() deallocates it using the C++ delete operator, causing heap metadata corruption. Attackers can trigger this memory management mismatch to cause denial of service through process crashes or potentially achieve arbitrary code execution depending on allocator state.</t>
+          <t>Elasticsearch가 업로드된 기계 학습 모델을 평가하는 데 사용하는 기본 추론 프로세스는 오프셋이 기본 스토리지의 경계 내에 있는지 확인하지 않고 모델 내부에 제공된 오프셋에서 메모리 주소를 계산하는 모델 작업을 허용합니다. 학습된 모델을 업로드하고 배포하는 데 필요한 권한이 있는 사용자는 의도된 할당 외부의 메모리를 읽고 쓰는 모델을 만들 수 있습니다. 그 결과 추론 프로세스를 중단시키는 힙 손상이 발생하며, 힙 레이아웃을 충분히 제어하면 해당 프로세스의 컨텍스트에서 임의 코드 실행이 허용될 수 있습니다.</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/Vladimir-tokarev-cyera/llama-cpp-security-patches</t>
+          <t>https://discuss.elastic.co/t/elasticsearch-8-19-20-9-4-5-9-5-1-security-update-esa-2026-123/389504</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -919,29 +919,29 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>pypi</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20260901001242</t>
+          <t>20260901225433</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>CVE-2026-43627</t>
+          <t>CVE-2026-72649</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>llama.cpp</t>
+          <t>Elasticsearch</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>ggml.ai</t>
+          <t>Elastic</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -957,22 +957,22 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>CVSS:3.1/AV:L/AC:L/PR:N/UI:R/S:U/C:H/I:H/A:H</t>
+          <t>CVSS:3.1/AV:N/AC:L/PR:L/UI:N/S:U/C:H/I:H/A:H</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20260806</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -982,12 +982,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>[버전범위 불명확] llama.cpp builds b1283 through b9058 contain an integer overflow vulnerability in the llama_batch_init() function where unchecked multiplications in malloc() calls can wrap past INT32_MAX when computing allocation sizes. Attackers can pass specially crafted parameters to trigger integer overflow, causing heap corruption and potentially achieving arbitrary code execution through subsequent batch operations that write past allocated buffer boundaries.</t>
+          <t>[버전범위 불명확] Deserialization of Untrusted Data (CWE-502) in the Elasticsearch machine learning component can lead to remote code execution via Object Injection (CAPEC-586). A specially crafted trained model artifact could cause attacker-controlled logic to execute with a materially broader system-call surface than intended. Exploitation requires an authenticated user with sufficient privileges to create and deploy trained models.</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/Vladimir-tokarev-cyera/llama-cpp-security-patches</t>
+          <t>https://discuss.elastic.co/t/elasticsearch-8-19-20-9-4-5-9-5-1-security-update-esa-2026-114/390087</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,37 +997,41 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>pypi</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20260901001242</t>
+          <t>20260901225433</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>CVE-2026-43628</t>
+          <t>CVE-2026-77068</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>llama.cpp</t>
+          <t>n8n</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>ggml.ai</t>
+          <t>n8n</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr"/>
+          <t>&gt;=2.33.0,&lt;2.33.4|==2.34.0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2.33.4</t>
+        </is>
+      </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -1035,22 +1039,22 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>CVSS:3.1/AV:L/AC:L/PR:N/UI:R/S:U/C:H/I:H/A:H</t>
+          <t>CVSS:3.1/AV:N/AC:L/PR:L/UI:N/S:U/C:H/I:H/A:H</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20260806</t>
+          <t>20260820</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1060,12 +1064,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>[버전범위 불명확] llama.cpp builds b3978 through b9058 contain an integer underflow and out-of-bounds read vulnerability in the DRY sampler that allows unauthenticated attackers to trigger a heap buffer underflow by sending a crafted HTTP request with dry_allowed_length set to INT32_MIN to the /v1/completions or /v1/chat/completions endpoints. Attackers can exploit this vulnerability to crash the server with SIGSEGV causing denial of service for all connected users, or corrupt token sampling probabilities by reading garbage values from memory before the allocated buffer.</t>
+          <t>2.33.4 이전의 n8n과 2.34.1 이전의 2.34.x에는 MCP 노드-스키마 로딩에 사용되는 @n8n/workflow-sdk 노드-스키마 로더의 원격 코드 실행 취약점이 포함되어 있습니다. 로더는 경로 순회 시퀀스의 유효성을 검사하지 않고 공격자가 제공한 노드 유형 문자열에서 직접 노드의 스키마 모듈 경로를 파생합니다. global:member 권한이 있는 인증된 사용자는 경로 탐색을 통해 악성 파일을 참조하여 n8n 기본 프로세스에서 코드가 실행될 수 있습니다.</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/Vladimir-tokarev-cyera/llama-cpp-security-patches</t>
+          <t>https://github.com/n8n-io/n8n/security/advisories/GHSA-6h4x-896x-fw5m</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1075,37 +1079,41 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>npm</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20260901001242</t>
+          <t>20260901225433</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>CVE-2026-70638</t>
+          <t>CVE-2026-77079</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>llama.cpp</t>
+          <t>n8n</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>ggml.ai</t>
+          <t>n8n</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr"/>
+          <t>&lt;2.33.4|==2.34.0</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2.33.4</t>
+        </is>
+      </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -1113,22 +1121,22 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>CVSS:3.1/AV:L/AC:L/PR:N/UI:R/S:U/C:H/I:H/A:H</t>
+          <t>CVSS:3.1/AV:N/AC:L/PR:L/UI:N/S:U/C:H/I:H/A:H</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20260806</t>
+          <t>20260820</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1138,12 +1146,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>[버전범위 불명확] llama.cpp builds b1886 through b7445 contain an integer overflow vulnerability in the LLaMA-Android JNI wrapper where the new_1batch() function multiplies sizeof(llama_seq_id) by an attacker-controlled n_seq_max parameter without overflow validation, causing heap buffer allocation to wrap and allocate insufficient memory. Attackers can exploit this by providing a crafted n_seq_max value through a malicious model file or JNI call to trigger heap corruption and achieve denial of service or arbitrary code execution on Android applications using the LLaMA-Android binding.</t>
+          <t>2.34.1 및 2.33.4 이전의 n8n에는 사용자 정의 프로젝트 역할 삭제(재할당) 경로에 인증 우회가 포함되어 있습니다. 재할당 대상이 있는 사용자 지정 프로젝트 역할을 삭제할 때 코드는 대상 역할이 존재하고 프로젝트 범위에 해당하는지만 확인했으며 프로젝트 수준 권한 부여 확인은 수행하지 않았습니다. 좁은 역할:manageProject 전역 범위만 보유한 사용자는 인스턴스에서 사용 중인 모든 사용자 지정 프로젝트 역할을 삭제하고 해당 소유자(자신 포함)를 기본 제공 프로젝트:관리자 역할에 다시 할당하여 합법적인 액세스 권한이 없는 프로젝트에 대한 전체 관리 제어 권한을 얻을 수 있습니다.</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/Vladimir-tokarev-cyera/llama-cpp-security-patches</t>
+          <t>https://github.com/n8n-io/n8n/security/advisories/GHSA-xhmh-8fgr-xqhj</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1153,19 +1161,19 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>npm</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20260901001242</t>
+          <t>20260901225433</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>CVE-2026-72763</t>
+          <t>CVE-2026-77080</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1175,12 +1183,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>n8n GmbH</t>
+          <t>n8n</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>&lt;2.32.1</t>
+          <t>&lt;1.123.69|&gt;=2.0.0,&lt;2.33.4|==2.34.0</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -1191,22 +1199,22 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>CVSS:4.0/AV:N/AC:L/AT:P/PR:L/UI:N/VC:H/VI:N/VA:N/SC:H/SI:H/SA:L/E:X/CR:X/IR:X/AR:X/MAV:X/MAC:X/MAT:X/MPR:X/MUI:X/MVC:X/MVI:X/MVA:X/MSC:X/MSI:X/MSA:X/S:X/AU:X/R:X/V:X/RE:X/U:X</t>
+          <t>CVSS:3.1/AV:N/AC:L/PR:L/UI:N/S:U/C:H/I:H/A:H</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20260811</t>
+          <t>20260820</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1216,12 +1224,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>n8n before 1.123.67, 2.31.5, and 2.32.1 validates credential-access only for a node's top-level credentials and not for credentials referenced inside an Execute Sub-workflow node's inline workflow JSON. A member with Editor access to a shared workflow (when workflow sharing is enabled) who knows a target credential's ID can reference that credential in the inline JSON; it passes save-time and runtime validation and resolves in the parent workflow's project context, allowing the attacker to use or exfiltrate credentials they are not permitted to access.</t>
+          <t>1.123.69 이전의 n8n, 2.33.4 이전의 2.x, 2.34.1 이전의 2.34.x에는 Snowflake 노드의 임의 파일 읽기 및 쓰기 취약점이 포함되어 있습니다. 이 취약점은 n8n의 파일 액세스 제한을 적용하지 않고 클라이언트 측 명령을 포함한 자유 형식 쿼리 실행 입력을 Snowflake SDK에 직접 전달합니다. 사용 가능한 Snowflake 자격 증명이 있는 인증된 사용자는 n8n 호스트에서 로컬 파일을 업로드하거나 기존 파일을 준비된 파일로 덮어쓸 수 있습니다.</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/n8n-io/n8n/security/advisories/GHSA-cj9h-qx8g-pq2g</t>
+          <t>https://github.com/n8n-io/n8n/security/advisories/GHSA-r4j2-j3wm-q689</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1236,29 +1244,29 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20260901001242</t>
+          <t>20260901225433</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>CVE-2026-71211</t>
+          <t>CVE-2026-77084</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>MLflow</t>
+          <t>n8n</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>n8n</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>&gt;=3.13.0,&lt;=3.15.2</t>
+          <t>&lt;1.123.69|&gt;=2.0.0,&lt;2.33.4|==2.34.0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
@@ -1269,22 +1277,22 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>CVSS:3.1/AV:N/AC:L/PR:L/UI:N/S:U/C:H/I:L/A:N</t>
+          <t>CVSS:3.1/AV:N/AC:L/PR:L/UI:N/S:U/C:H/I:H/A:H</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20260805</t>
+          <t>20260820</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1294,52 +1302,56 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>MLflow AI Gateway permits SSRF through an unvalidated api_base MLflow's AI Gateway accepts an auth_config.api_base value when creating a gateway secret (mlflow/server/handlers.py, _create_gateway_secret) with no validation of scheme, host, or IP range; the value is stored verbatim. The gateway proxy endpoint (mlflow/server/gateway_api.py, raw_proxy) subsequently issues an HTTP request to that stored api_base plus a caller-supplied path and returns the full response body. MLflow's existing SSRF guard, _validate_webhook_url (which blocks non-global and metadata IPs), is never invoked anywhere in this gateway secret/proxy code path. The CreateGatewaySecret action additionally has no entry in the permission-validator map, so it requires only basic authentication rather than any specific scope, meaning any authenticated user — including read-only accounts — can create a secret pointing at an internal address and reach it via the proxy endpoint, potentially exposing cloud-instance IAM creden</t>
+          <t>1.123.69 이전의 n8n(및 2.33.4/2.34.1 이전의 2.x)에는 Git 노드의 코드 실행 취약점이 포함되어 있습니다. Git 노드는 특정 저장소-로컬 git 구성 값을 무력화하지 않고 실행했으므로 악의적인 값이 포함된 저장소에 대한 후속 Git 노드 작업은 이를 n8n 프로세스 사용자로 실행합니다. 이는 Git 노드의 자체 구성 제어를 통해서는 도달할 수 없으며 악의적인 값을 심기 위해서는 다른 곳에 별도의 파일 쓰기 취약점이 필요합니다.</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/advisories/GHSA-h7x2-h6g9-p789</t>
+          <t>https://github.com/n8n-io/n8n/security/advisories/GHSA-m87g-qr43-ccvc</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>OSV+GHSA</t>
+          <t>NVD</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>pypi</t>
+          <t>npm</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20260901001336</t>
+          <t>20260901225433</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>CVE-2026-72749</t>
+          <t>CVE-2026-84304</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>n8n</t>
+          <t>gRPC</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>n8n GmbH</t>
+          <t>gRPC Authors</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>&lt;2.32.1</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr"/>
+          <t>&lt;1.83.1</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1.83.1</t>
+        </is>
+      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -1347,22 +1359,22 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>CVSS:4.0/AV:N/AC:L/AT:N/PR:L/UI:N/VC:N/VI:N/VA:H/SC:N/SI:N/SA:N/E:X/CR:X/IR:X/AR:X/MAV:X/MAC:X/MAT:X/MPR:X/MUI:X/MVC:X/MVI:X/MVA:X/MSC:X/MSI:X/MSA:X/S:X/AU:X/R:X/V:X/RE:X/U:X</t>
+          <t>CVSS:4.0/AV:N/AC:L/AT:N/PR:N/UI:N/VC:N/VI:N/VA:H/SC:N/SI:N/SA:N/E:X/CR:X/IR:X/AR:X/MAV:X/MAC:X/MAT:X/MPR:X/MUI:X/MVC:X/MVI:X/MVA:X/MSC:X/MSI:X/MSA:X/S:X/AU:X/R:X/V:X/RE:X/U:X</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20260811</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1372,12 +1384,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>n8n before 1.123.67, 2.31.5, and 2.32.1 contains a prototype pollution vulnerability in the Edit Fields (Set) node. The node assigns output fields via a dot-notation path setter without restricting the field name, allowing an authenticated user to name a field after an inherited built-in method path and corrupt a shared global in the main Node.js process. Because that global is used on the request-authentication path, the instance then fails every authenticated request, causing an instance-wide denial of service for all users until the process is restarted.</t>
+          <t>gRPC-Go is the Go language implementation of gRPC. Prior to 1.83.1, internal/transport/transport.go stores each fragmented HTTP/2 DATA frame as a separate recvMsg in recvBuffer, so millions of one-byte frames can consume disproportionate heap memory even when payload bytes remain within connection and stream flow-control windows. An unauthenticated remote attacker can use concurrent multiplexed streams to exhaust process memory and cause a runtime panic or out-of-memory termination. Receive-buffer compaction is enabled by default and can be controlled temporarily with GRPC_GO_EXPERIMENTAL_ENABLE_RECEIVE_BUFFER_COMPACTION. This issue is fixed in version 1.83.1.</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/n8n-io/n8n/security/advisories/GHSA-xwx6-jjhv-84p8</t>
+          <t>https://github.com/grpc/grpc-go/commit/7354d9c8debb4bcf2225bf429857078de310c176</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1387,19 +1399,19 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>npm</t>
+          <t>pypi</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20260901001242</t>
+          <t>20260901225433</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>CVE-2026-72770</t>
+          <t>CVE-2026-72768</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1409,15 +1421,19 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>n8n GmbH</t>
+          <t>n8n</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>&lt;1.123.67</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr"/>
+          <t>&gt;=2.31.0,&lt;2.31.5|==2.32.0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2.31.5</t>
+        </is>
+      </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -1425,12 +1441,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>CVSS:4.0/AV:N/AC:L/AT:N/PR:L/UI:N/VC:H/VI:N/VA:N/SC:N/SI:N/SA:N/E:X/CR:X/IR:X/AR:X/MAV:X/MAC:X/MAT:X/MPR:X/MUI:X/MVC:X/MVI:X/MVA:X/MSC:X/MSI:X/MSA:X/S:X/AU:X/R:X/V:X/RE:X/U:X</t>
+          <t>CVSS:3.1/AV:N/AC:L/PR:L/UI:N/S:U/C:H/I:H/A:L</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1440,7 +1456,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1450,12 +1466,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>n8n versions before 1.123.67 contain a path traversal vulnerability in the Git node's fetch, pull, and push-tags operations that allows authenticated users to bypass repository-path containment checks. Attackers with workflow create/execute rights can point allowlisted remote configurations at local paths outside the sandbox to pull arbitrary git repositories and read their files and history.</t>
+          <t>n8n versions before 2.32.1 contain a server-side request forgery protection bypass vulnerability in the MCP Client node that allows authenticated users to bypass SSRF protections. Attackers can craft workflows that send requests to internal or blocked hosts without routing through SSRF protection, exposing internal services and reading responses back through the workflow.</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/n8n-io/n8n/security/advisories/GHSA-gf29-4f56-r2jf</t>
+          <t>https://github.com/n8n-io/n8n/security/advisories/GHSA-vhf8-cg2h-cg3p</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1470,32 +1486,36 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20260901001242</t>
+          <t>20260901225433</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>CVE-2026-70640</t>
+          <t>CVE-2026-72773</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>llama.cpp</t>
+          <t>n8n</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>ggml.ai</t>
+          <t>n8n</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>*</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr"/>
+          <t>&lt;2.31.5|==2.32.0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2.31.5</t>
+        </is>
+      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
           <t>HIGH</t>
@@ -1503,22 +1523,22 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>CVSS:3.1/AV:L/AC:H/PR:N/UI:R/S:U/C:H/I:H/A:H</t>
+          <t>CVSS:3.1/AV:N/AC:L/PR:L/UI:N/S:C/C:H/I:N/A:N</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20260806</t>
+          <t>20260811</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1528,12 +1548,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>[버전범위 불명확] llama.cpp builds b1886 through b7445 contain a race condition use-after-free vulnerability in the LLaMA-Android JNI wrapper where bench_1model() and free_1context() lack synchronization, allowing Thread A to operate on freed memory while Thread B concurrently frees the llama_context. Attackers can exploit this by performing heap spray with attacker-controlled data containing a fake vtable to hijack the vtable pointer at offset +0x30, causing llama_batch_allocr::clear() to dereference arbitrary memory and achieve remote code execution.</t>
+          <t>n8n before 2.31.5 and 2.32.x before 2.32.1 contain a path-confinement bypass in the @n8n/computer-use file-search (search_files) tool. A crafted search pattern can bypass the base-directory confinement check and expand to locations outside the configured directory, causing the tool to return the names and contents of arbitrary local files readable by the daemon's OS user. Any deployment where an actor can influence the tool's search input is affected.</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/Vladimir-tokarev-cyera/llama-cpp-security-patches</t>
+          <t>https://github.com/n8n-io/n8n/security/advisories/GHSA-pf2q-pxhf-hgmw</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1543,60 +1563,60 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>npm</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20260901001242</t>
+          <t>20260901225433</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>CVE-2026-37009</t>
+          <t>CVE-2026-77072</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>CrewAI</t>
+          <t>n8n</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>CrewAI</t>
+          <t>n8n</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>&lt;1.123.69|&gt;=2.33.0,&lt;2.33.4|==2.34.0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>CVSS:3.1/AV:N/AC:L/PR:N/UI:N/S:U/C:L/I:L/A:N</t>
+          <t>CVSS:3.1/AV:N/AC:L/PR:L/UI:R/S:C/C:H/I:L/A:N</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20260827</t>
+          <t>20260820</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1606,12 +1626,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>[버전범위 불명확] A SQL injection vulnerability in NL2SQLTool in crewai-tools v1.10.2rc1 allows a remote attacker to execute arbitrary SQL commands via an unsanitized sql_query argument.</t>
+          <t>1.123.69, 2.33.4 및 2.34.1 이전의 n8n에는 양식 노드의 완료 페이지에 저장된 교차 사이트 스크립팅 취약점이 포함되어 있습니다. 완료 페이지는 responseWith가 '리디렉션'으로 설정되지 않은 경우에만 샌드박싱 Content-Security-Policy를 적용했지만 responseText는 항상 원시 HTML로 렌더링되었습니다. 인증된 구성원은 responseText를 채운 상태로 표현식을 통해 '리디렉션'으로 responseWith를 설정할 수 있으며, 이로 인해 완료 페이지가 n8n 원본에서 정리되지 않은 HTML 및 스크립트를 제공하게 됩니다. 결과 공개 양식을 제출한 모든 방문자는 해당 스크립트가 세션과 동일한 출처를 실행하게 됩니다.</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>http://crewaiinc.com</t>
+          <t>https://github.com/n8n-io/n8n/security/advisories/GHSA-rmr5-775f-jvm2</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1621,60 +1641,60 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>pypi</t>
+          <t>npm</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>20260901001242</t>
+          <t>20260901225433</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>CVE-2026-43630</t>
+          <t>CVE-2026-77077</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>llama.cpp</t>
+          <t>n8n</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>ggml.ai</t>
+          <t>n8n</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>&lt;1.123.69|&gt;=2.33.0,&lt;2.33.4|==2.34.0</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>CVSS:3.1/AV:N/AC:L/PR:N/UI:N/S:U/C:L/I:N/A:L</t>
+          <t>CVSS:3.1/AV:N/AC:L/PR:L/UI:N/S:U/C:H/I:L/A:L</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20260806</t>
+          <t>20260820</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1684,12 +1704,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>[버전범위 불명확] llama.cpp builds b5702 through b7653 contain an out-of-bounds read vulnerability in the recurrent memory state restore path that allows attackers with write access to the slot save directory to read memory past the end of the allocated cells array. Attackers can craft a malicious slot file with an oversized seq_id value to trigger an out-of-bounds read that leaks heap data including pointer values into server logs, defeating ASLR protections and facilitating further exploitation.</t>
+          <t>1.123.69, 2.33.4 및 2.34.1 이전의 n8n 버전에는 JavaScript 작업 실행기 VM 샌드박스 이스케이프가 포함되어 있습니다. 러너의 프로토타입 동결 루틴은 globalThis 함수를 다루지만 EventEmitter와 같은 내부 모듈 생성자는 다루지 않으므로 코드 노드 액세스 권한이 있는 인증된 사용자가 프로토타입 오염을 이용하여 러너 컨테이너 내에서 임의의 명령을 실행할 수 있습니다. 오염된 프로토타입은 프로세스 전체 개체이기 때문에 동일한 공유 실행기에서 다른 테넌트의 코드 노드 실행 전반에 걸쳐 손상이 지속됩니다. 작업 실행기가 활성화되지 않은 v1.x 인스턴스에서는 코드 노드 JavaScript가 기본 n8n 프로세스에서 직접 실행되므로 영향이 더 커질 수 있습니다.</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/Vladimir-tokarev-cyera/llama-cpp-security-patches</t>
+          <t>https://github.com/n8n-io/n8n/security/advisories/GHSA-m3hg-p5r9-fg9h</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1699,60 +1719,60 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>github</t>
+          <t>npm</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20260901001242</t>
+          <t>20260901225433</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>CVE-2026-72768</t>
+          <t>CVE-2026-52130</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>n8n</t>
+          <t>llama.cpp</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>n8n GmbH</t>
+          <t>ggml.ai</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>&lt;2.32.1</t>
+          <t>*</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr"/>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>CVSS:4.0/AV:N/AC:L/AT:N/PR:L/UI:N/VC:L/VI:N/VA:N/SC:H/SI:H/SA:L/E:X/CR:X/IR:X/AR:X/MAV:X/MAC:X/MAT:X/MPR:X/MUI:X/MVC:X/MVI:X/MVA:X/MSC:X/MSI:X/MSA:X/S:X/AU:X/R:X/V:X/RE:X/U:X</t>
+          <t>CVSS:3.1/AV:N/AC:L/PR:N/UI:N/S:U/C:N/I:N/A:H</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20260811</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1762,12 +1782,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>n8n versions before 2.32.1 contain a server-side request forgery protection bypass vulnerability in the MCP Client node that allows authenticated users to bypass SSRF protections. Attackers can craft workflows that send requests to internal or blocked hosts without routing through SSRF protection, exposing internal services and reading responses back through the workflow.</t>
+          <t>[버전범위 불명확] llama.cpp b5693 and before is vulnerable to Uncontrolled Recursion in common/json-schema-to-grammar.cpp, resulting in a denial of service.</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/n8n-io/n8n/security/advisories/GHSA-vhf8-cg2h-cg3p</t>
+          <t>https://blog.ph4nt0m.xyz/ko/cves/cve-2026-52130/</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1777,60 +1797,60 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>npm</t>
+          <t>github</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20260901001242</t>
+          <t>20260901225433</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>CVE-2026-72775</t>
+          <t>CVE-2026-47628</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>n8n</t>
+          <t>Triton Inference Server</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>n8n GmbH</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>&lt;2.32.1</t>
+          <t>&lt;=26.05</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>CVSS:4.0/AV:N/AC:L/AT:P/PR:L/UI:N/VC:N/VI:N/VA:N/SC:H/SI:H/SA:H/E:X/CR:X/IR:X/AR:X/MAV:X/MAC:X/MAT:X/MPR:X/MUI:X/MVC:X/MVI:X/MVA:X/MSC:X/MSI:X/MSA:X/S:X/AU:X/R:X/V:X/RE:X/U:X</t>
+          <t>CVSS:3.1/AV:N/AC:L/PR:N/UI:N/S:U/C:N/I:N/A:H</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20260811</t>
+          <t>20260818</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1840,12 +1860,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>n8n before 1.123.67, 2.31.5, and 2.32.1 contains a SQL injection vulnerability in the PostgresTrigger node, which interpolates user-supplied identifier parameters (channel, function, and trigger names) into SQL statements without proper escaping. An authenticated user can inject arbitrary SQL executed against the connected PostgreSQL database with the configured credential's privileges, allowing full read and write access.</t>
+          <t>Linux용 NVIDIA Triton 추론 서버에는 공격자가 제한 없이 리소스를 할당할 수 있는 취약점이 포함되어 있습니다. 공격이 성공하면 서비스 거부가 발생할 수 있습니다.</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/n8n-io/n8n/security/advisories/GHSA-jqwr-vx3p-r266</t>
+          <t>https://github.com/NVIDIA/product-security/tree/main/2026/5865</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1855,60 +1875,60 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>npm</t>
+          <t>github</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20260901001242</t>
+          <t>20260901225433</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>CVE-2026-70639</t>
+          <t>CVE-2026-47629</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>llama.cpp</t>
+          <t>Triton Inference Server</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>ggml.ai</t>
+          <t>nvidia</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>&lt;=26.05</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>CVSS:3.1/AV:L/AC:L/PR:N/UI:R/S:U/C:N/I:N/A:H</t>
+          <t>CVSS:3.1/AV:N/AC:L/PR:N/UI:N/S:U/C:N/I:N/A:H</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20260806</t>
+          <t>20260818</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>20260831</t>
+          <t>20260901</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1918,12 +1938,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>[버전범위 불명확] llama.cpp builds b1886 through b7445 contain a null pointer dereference vulnerability in the LLaMA-Android JNI wrapper where the bench_1model() function fails to validate the model context pointer before dereferencing it. Attackers can supply a malicious, corrupt, or truncated model file to trigger a null context condition, causing a SIGSEGV crash that terminates the Android application process and results in denial of service.</t>
+          <t>Linux용 NVIDIA Triton 추론 서버에는 공격자가 부적절한 입력 유효성 검사를 유발할 수 있는 취약점이 포함되어 있습니다. 공격이 성공하면 서비스 거부가 발생할 수 있습니다.</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>https://github.com/Vladimir-tokarev-cyera/llama-cpp-security-patches</t>
+          <t>https://github.com/NVIDIA/product-security/tree/main/2026/5865</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -1938,85 +1958,2609 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20260901001242</t>
+          <t>20260901225433</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>CVE-2026-72773</t>
+          <t>CVE-2026-41523</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
+          <t>vLLM</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>vllm</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>&lt;0.22.0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0.22.0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>7.5</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>CVSS:3.1/AV:N/AC:H/PR:N/UI:R/S:U/C:H/I:H/A:H</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>20260622</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>20260901</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>vLLM은 LLM(대형 언어 모델)을 위한 추론 및 제공 엔진입니다. 0.22.0 이전에는 vLLM 활성화 함수 로딩의 어설션 기반 보안 검사를 통해 vLLM이 Python 최적화 모드(python -O 또는 PYTHONOPTIMIZE=1)에서 실행될 때 인증되지 않은 공격자가 악의적인 HuggingFace 모델을 게시하여 서버에서 임의 코드 실행을 달성할 수 있었습니다. 이 취약점은 0.22.0에서 수정되었습니다.</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/vllm-project/vllm/commit/b3c7ffcab82c2439726f8cb213800f6f38c023d3</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>NVD+OSV+GHSA</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>pypi</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>20260901225524</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>CVE-2026-45360</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Airflow</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Apache Software Foundation</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>&gt;=3.2.0,&lt;3.2.2</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>3.2.2</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>CVSS:3.1/AV:N/AC:L/PR:N/UI:N/S:U/C:L/I:L/A:L</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>20260601</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>20260901</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>Apache Airflow Vulnerable to Deserialization of Untrusted Data Apache Airflow's scheduler-side deadline-reference decoder (`SerializedCustomReference.deserialize_reference`) imported and dispatched arbitrary class paths drawn from DAG-author-controlled serialized state without an allowlist or plugin-registry gate. A DAG author whose code reaches the scheduler — the default on single-host deployments where the DAG bundle is importable from the scheduler process — could embed a custom `DeadlineReference` whose serialized form named an attacker-controlled module path, causing the scheduler to `import_string(...)` and instantiate that class with a live SQLAlchemy session attached. Affects deployments where DAG-author code is less trusted than the scheduler process. Users are advised to upgrade to `apache-airflow` 3.2.2 or later.</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/advisories/GHSA-2r5m-76wx-56gx</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>OSV+GHSA</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>pypi</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>20260901225524</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>CVE-2026-77075</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>n8n</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>n8n GmbH</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>&lt;2.31.5|&lt;2.32.1</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr"/>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>n8n</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1.123.69|&gt;=2.33.0,&lt;2.33.4|==2.34.0</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>CVSS:3.1/AV:N/AC:L/PR:L/UI:R/S:U/C:H/I:H/A:N</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>20260820</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>20260901</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>1.123.69 이전의 n8n, 2.33.4 이전의 2.x, 2.34.1 이전의 2.34.x에는 리소스 로케이터 필드 링크 미리 보기 렌더링에 표현식 삽입 취약점이 포함되어 있습니다. 편집기는 표현식 구문을 확인하지 않고 필드의 저장된 값을 노드 유형의 URL 템플릿에 직접 연결했습니다. 인증된 구성원은 악의적인 값을 저장할 수 있으므로 다른 사용자가 편집기에서 영향을 받은 노드를 열면 삽입된 표현식이 피해자의 인증된 세션(교차 사용자 스크립트 실행)에서 JavaScript로 평가됩니다.</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/n8n-io/n8n/security/advisories/GHSA-fh4c-9rr2-p7qc</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>NVD</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>npm</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>20260901225433</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>CVE-2026-77081</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>n8n</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>n8n</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1.123.69|&gt;=2.0.0,&lt;2.33.4|==2.34.0</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>CVSS:3.1/AV:N/AC:L/PR:L/UI:N/S:U/C:H/I:L/A:N</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>20260820</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>20260901</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>1.123.69 이전의 n8n, 2.33.4 이전의 2.x, 2.34.1 이전의 2.x에는 GraphQL 노드에 허용된 도메인 우회가 포함되어 있습니다. 노드의 인증 매개변수가 표현식 모드로 설정되면 모든 인증 기반 자격 증명 선택기가 활성으로 처리됩니다. 서로 다른 유형의 두 가지 자격 증명이 연결된 경우 노드는 두 자격 증명 모두의 자료를 계속 연결하면서 첫 번째 자격 증명에만 허용 도메인 정책을 적용합니다. 워크플로 작성 권한이 있는 인증된 사용자는 도메인 제한 자격 증명을 공격자가 제어하는 ​​엔드포인트로 보내고 유출된 자격 증명의 권한으로 이를 유출할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/n8n-io/n8n/security/advisories/GHSA-wcv8-x773-j96r</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>NVD</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>npm</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>20260901225433</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>CVE-2026-9856</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Transformers</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Hugging Face</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>&lt;5.10.0</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>5.10.0</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>CVSS:3.0/AV:N/AC:L/PR:N/UI:R/S:U/C:N/I:H/A:L</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>20260802</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>20260901</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Transformers save_pretrained path traversal allows arbitrary file writes through chat template names A vulnerability in huggingface/transformers versions &lt; 5.10.0 allows an attacker to perform arbitrary file writes via path traversal. The issue resides in the `save_pretrained()` methods of `PreTrainedTokenizerBase` and `ProcessorMixin`, where keys from the `chat_template` dictionary are used directly as filenames without proper validation. An attacker can exploit this by publishing a malicious Hugging Face Hub repository with a crafted `tokenizer_config.json` file. When a victim downloads and saves the tokenizer or processor, the attacker-controlled keys can escape the intended save directory, enabling arbitrary file writes with attacker-controlled content. This vulnerability affects multiple processors inheriting from `ProcessorMixin`, including Idefics, Florence, Gemma, Phi, and Qwen-VL.</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/advisories/GHSA-xrqw-3rrv-vx5w</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>OSV+GHSA</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>pypi</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>20260901225524</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>CVE-2026-4137</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>MLflow</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>&gt;=1.26.0,&lt;3.11.0</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>3.11.0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>CVSS:3.0/AV:L/AC:H/PR:L/UI:N/S:U/C:H/I:H/A:H</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>20260518</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>20260901</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>MLFlow Creates a Temporary File With Insecure Permissions In mlflow/mlflow versions prior to 3.11.0, the `get_or_create_nfs_tmp_dir()` function in `mlflow/utils/file_utils.py` creates temporary directories with world-writable permissions (0o777), and the `_create_model_downloading_tmp_dir()` function in `mlflow/pyfunc/__init__.py` creates directories with group-writable permissions (0o770). These insecure permissions allow local attackers to tamper with model artifacts, such as cloudpickle-serialized Python objects, and achieve arbitrary code execution when the tampered artifacts are deserialized via `cloudpickle.load()`. This vulnerability is particularly critical in environments with shared NFS mounts, such as Databricks, where NFS is enabled by default. The issue is a continuation of the vulnerability class addressed in CVE-2025-10279, which was only partially fixed.</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/advisories/GHSA-f2m9-wcf4-cwwx</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>OSV+GHSA</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>pypi</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>20260901225524</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>CVE-2026-72636</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Elasticsearch</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>elastic</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>&gt;=8.0.0,&lt;8.19.20|&gt;=9.0.0,&lt;9.4.5</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>CVSS:3.1/AV:N/AC:L/PR:L/UI:N/S:U/C:N/I:N/A:H</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>20260813</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>20260901</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>Elasticsearch 와일드카드 일치 도우미의 제어되지 않은 재귀(CWE-674)는 과도한 할당(CAPEC-130)을 통해 서비스 거부로 이어질 수 있습니다. 이름에 대한 와일드카드 패턴을 확인하는 데 사용되는 매처는 재귀적으로 구현되며 재귀 깊이나 수행되는 총 일치 작업 수에 대한 제한이 없습니다. 충분히 긴 이름에 대해 평가된 다수의 와일드카드 그룹이 있는 와일드카드 패턴을 포함하는 검색 요청은 스레드 스택을 소모합니다. Elasticsearch는 스택 오버플로를 복구할 수 없는 조건으로 처리하고 노드를 종료하므로 요청은 정상적으로 실패하지 않고 영향을 받은 노드를 종료합니다.</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>https://discuss.elastic.co/t/elasticsearch-8-19-20-9-4-5-security-update-esa-2026-133/389499</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>NVD</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>pypi</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>20260901225433</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>CVE-2026-72638</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Elasticsearch</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>elastic</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>&gt;=8.0.0,&lt;8.19.20|&gt;=9.0.0,&lt;9.4.5</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>CVSS:3.1/AV:N/AC:L/PR:L/UI:N/S:U/C:N/I:N/A:H</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>20260813</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>20260901</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>Elasticsearch의 통제되지 않은 재귀(CWE-674)는 입력 데이터 조작(CAPEC-153)을 통해 서비스 거부로 이어질 수 있습니다. 낮은 권한의 인덱스 생성 권한만 보유한 인증된 사용자는 주기 또는 깊이 검사 없이 재귀적으로 해결되어 스레드 스택을 소진하고 영향을 받는 노드를 종료하는 특수 제작되고 잘못된 형식의 사용자 지정 분석 정의가 포함된 단일 요청을 제출할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>https://discuss.elastic.co/t/elasticsearch-8-19-20-9-4-5-security-update-esa-2026-119/389498</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>NVD</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>pypi</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>20260901225433</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>CVE-2026-72639</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Elasticsearch</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>elastic</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>&gt;=8.19.0,&lt;8.19.20|&gt;=9.3.0,&lt;9.4.5|&gt;=9.5.0,&lt;9.5.1</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>CVSS:3.1/AV:N/AC:L/PR:L/UI:N/S:U/C:N/I:N/A:H</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>20260813</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>20260901</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>Elasticsearch는 검색 강조 표시 옵션에서 허용하는 사용자 제공 개수에 상한을 적용하지 않으며, 해당 개수에서 파생된 할당은 회로 차단기에 대해 고려되지 않습니다. 단일 검색 가능 인덱스에 대해 읽기 권한만 보유한 인증된 사용자는 노드가 지나치게 큰 내부 데이터 구조를 예약하게 만드는 작은 검색 요청을 제출할 수 있습니다. 기존 강조 표시 안전 한도가 평가되기 전에 할당이 발생하므로 메모리 소모로 인해 Elasticsearch 노드 프로세스가 종료되는 치명적인 오류가 발생합니다. 이로 인해 영향을 받은 노드에 대한 서비스 거부가 발생하고 클러스터 라우팅 및 상태가 저하됩니다. 결함은 체적이 아니며 인덱싱된 데이터의 크기에 의존하지 않으므로 단일 요청으로 충분합니다.</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>https://discuss.elastic.co/t/elasticsearch-8-19-20-9-4-5-9-5-1-security-update-esa-2026-120/389503</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>NVD</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>pypi</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>20260901225433</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>CVE-2026-72645</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Elasticsearch</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>elastic</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>&gt;=8.0.0,&lt;8.19.20|&gt;=9.0.0,&lt;9.4.5|&gt;=9.5.0,&lt;9.5.1</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>CVSS:3.1/AV:N/AC:L/PR:L/UI:N/S:U/C:N/I:N/A:H</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>20260813</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>20260901</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>Elasticsearch에서 과도한 크기 값(CWE-789)을 사용한 메모리 할당은 과도한 할당(CAPEC-130)을 통해 서비스 거부로 이어질 수 있습니다. 단일 인덱스에 대해 읽기 권한만 보유하고 있는 인증된 사용자는 과도하게 큰 메모리 할당을 유발하여 JVM 힙을 소진하고 영향을 받는 노드를 종료시키는 특수하게 조작된 작은 검색 요청 하나를 제출할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>https://discuss.elastic.co/t/elasticsearch-8-19-20-9-4-5-9-5-1-security-update-esa-2026-116/389502</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>NVD</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>pypi</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>20260901225433</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>CVE-2026-72647</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Elasticsearch</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>elastic</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>&gt;=8.0.0,&lt;8.19.20|&gt;=9.0.0,&lt;9.4.5</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>CVSS:3.1/AV:N/AC:L/PR:L/UI:N/S:U/C:N/I:N/A:H</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>20260813</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>20260901</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>Elasticsearch의 통제되지 않은 재귀(CWE-674)는 중첩 페이로드가 포함된 직렬화된 데이터(CAPEC-230)를 통해 서비스 거부로 이어질 수 있습니다. 단일 인덱스에 대해 읽기 권한만 보유한 인증된 사용자는 깊게 중첩된 구조가 깊이 제한 없이 처리되어 스레드 스택이 소진되고 영향을 받은 노드가 종료되는 특수 제작된 검색 요청 하나를 제출할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>https://discuss.elastic.co/t/elasticsearch-8-19-20-9-4-5-9-5-1-security-update-esa-2026-118/389497</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>NVD</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>pypi</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>20260901225433</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>CVE-2026-72678</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Elasticsearch</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>elastic</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>&gt;=8.19.0,&lt;8.19.20|&gt;=9.4.0,&lt;9.4.5|&gt;=9.5.0,&lt;9.5.1</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>CVSS:3.1/AV:N/AC:L/PR:L/UI:N/S:U/C:N/I:N/A:H</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>20260813</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>20260901</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>Elasticsearch는 내부 데이터 구조를 위한 메모리를 예약하는 데 해당 값이 사용되기 전에는 사용자 제공 입력에서 가져온 크기 값의 유효성을 검사하지 않습니다. 읽기 권한만 보유한 인증된 사용자는 노드가 지나치게 큰 할당을 시도하게 만드는 작은 단일 요청을 제품 API 엔드포인트에 제출할 수 있습니다. 결과적으로 메모리가 소진되면 Elasticsearch 노드 프로세스를 종료하는 치명적인 오류가 발생하여 영향을 받은 노드에 대한 서비스 거부가 발생하고 클러스터 상태가 저하됩니다. 결함은 체적 결함이 아니므로 대상 노드에 구성된 힙 크기에 관계없이 단일 요청으로 충분합니다.</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>https://discuss.elastic.co/t/elasticsearch-8-19-20-9-4-5-9-5-1-security-update-esa-2026-80/389507</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>NVD</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>pypi</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>20260901225433</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>CVE-2026-72679</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Elasticsearch</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>elastic</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>&gt;=8.19.0,&lt;8.19.20|&gt;=9.0.0,&lt;9.4.5</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>CVSS:3.1/AV:N/AC:L/PR:L/UI:N/S:U/C:N/I:N/A:H</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>20260813</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>20260901</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>Elasticsearch는 간격 쿼리에서 허용하는 사용자 제공 패턴에 구성 가능한 입력 길이 제한을 적용하지 않습니다. 깊게 중첩된 패턴을 컴파일하면 스레드 스택을 소진하고 치명적인 오류를 발생시키는 무제한 재귀가 발생하여 Elasticsearch 노드 프로세스가 종료되고 해당 노드에 대한 서비스 거부가 발생합니다. 단일 검색 가능 인덱스에 대해 읽기 전용 권한만 보유한 인증된 사용자는 하나의 작은 검색 요청으로 조건을 트리거할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>https://discuss.elastic.co/t/elasticsearch-8-19-20-9-4-5-security-update-esa-2026-81/389501</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>NVD</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>pypi</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>20260901225433</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>CVE-2026-72683</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Elasticsearch</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>elastic</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>&gt;=5.0.0,&lt;8.19.19|&gt;=9.3.0,&lt;9.3.8|&gt;=9.4.0,&lt;9.4.4</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>CVSS:3.1/AV:N/AC:L/PR:L/UI:N/S:U/C:N/I:N/A:H</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>20260813</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>20260901</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>Elasticsearch의 결함으로 인해 시뮬레이션 파이프라인 API 엔드포인트(https://www.elastic.co/docs/api/doc/elasticsearch/operation/operation-ingest-simulate)를 호출하는 데 필요한 권한이 있는 인증된 사용자가 자체 참조 데이터 구조를 생성하는 요청을 제출할 수 있습니다. 나중에 특정 내부 구성 요소가 해당 구조를 처리하면 작업이 제한 없이 반복되고 주변 실행 경로에서 처리되지 않는 치명적인 오류가 발생하여 영향을 받는 노드 프로세스가 종료되고 결과적으로 서비스 거부가 발생합니다.</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>https://discuss.elastic.co/t/elasticsearch-8-19-19-9-3-8-9-4-4-security-update-esa-2026-75/389496</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>NVD</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>pypi</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>20260901225433</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>CVE-2026-72684</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Elasticsearch</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>elastic</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>&gt;=8.0.0,&lt;8.19.20|&gt;=9.0.0,&lt;9.4.5</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>CVSS:3.1/AV:N/AC:L/PR:L/UI:N/S:U/C:N/I:N/A:H</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>20260813</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>20260901</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>Elasticsearch의 결함으로 인해 읽기 권한만 보유한 인증된 사용자가 조작된 사용자 제공 입력이 포함된 소규모 검색 요청을 제출할 수 있습니다. 해당 입력을 처리하면 특정 내부 구성 요소가 상한 없이 메모리를 할당하게 되며 할당은 이를 제한하려는 기존 메모리 계산 제어 범위 외부에서 발생합니다. 결과적인 메모리 부족 상태는 치명적이며 영향을 받은 노드 프로세스를 종료하여 서비스 거부를 유발합니다.</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>https://discuss.elastic.co/t/elasticsearch-8-19-20-9-4-5-security-update-esa-2026-76/389508</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>NVD</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>pypi</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>20260901225433</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>CVE-2026-72686</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Elasticsearch</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>elastic</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>&gt;=8.0.0,&lt;8.19.20|&gt;=9.0.0,&lt;9.4.5|&gt;=9.5.0,&lt;9.5.1</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>CVSS:3.1/AV:N/AC:L/PR:L/UI:N/S:U/C:N/I:N/A:H</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>20260813</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>20260901</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>Elasticsearch의 결함으로 인해 권한이 낮은 인증된 사용자가 조작된 사용자 제공 입력이 포함된 단일 요청을 제출할 수 있습니다. 특정 내부 구성 요소는 재귀 루틴을 사용하여 입력의 유효성을 검사하고 유효성이 검사되는 값의 길이에 제한을 적용하지 않으므로 유효성 검사로 인해 스레드가 해당 스택을 소모하게 됩니다. 결과적으로 발생한 치명적인 오류는 주변 실행 경로에서 처리되지 않고 영향을 받은 노드 프로세스를 종료하여 서비스 거부를 발생시킵니다.</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>https://discuss.elastic.co/t/elasticsearch-8-19-20-9-4-5-9-5-1-security-update-esa-2026-78/389505</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>NVD</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>pypi</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>20260901225433</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>CVE-2026-72687</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Elasticsearch</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>elastic</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>&gt;=8.0.0,&lt;8.19.20|&gt;=9.0.0,&lt;9.4.5|&gt;=9.5.0,&lt;9.5.1</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>CVSS:3.1/AV:N/AC:L/PR:L/UI:N/S:U/C:N/I:N/A:H</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>20260813</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>20260901</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>Elasticsearch의 결함으로 인해 권한이 낮은 인증된 사용자가 위조된 불투명 식별자가 포함된 작은 요청 하나를 제출할 수 있습니다. Elasticsearch는 식별자가 클러스터에서 합법적으로 발행되었는지 확인하기 전에 식별자를 디코딩하고 역직렬화하며, 식별자 내부에 전달된 크기 값은 사용 가능한 메모리 사용량 제어에 의해 제한되거나 설명되지 않는 할당을 구동합니다. 결과적인 메모리 부족 상태는 치명적이며 영향을 받은 노드 프로세스를 종료하여 서비스 거부를 초래합니다.</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>https://discuss.elastic.co/t/elasticsearch-8-19-20-9-4-5-9-5-1-security-update-esa-2026-79/389506</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>NVD</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>pypi</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>20260901225433</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>CVE-2026-72749</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>n8n</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>n8n</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1.123.67|&gt;=2.31.0,&lt;2.31.5|==2.32.0</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>CVSS:3.1/AV:N/AC:L/PR:L/UI:N/S:U/C:N/I:N/A:H</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>20260811</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>20260901</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>n8n before 1.123.67, 2.31.5, and 2.32.1 contains a prototype pollution vulnerability in the Edit Fields (Set) node. The node assigns output fields via a dot-notation path setter without restricting the field name, allowing an authenticated user to name a field after an inherited built-in method path and corrupt a shared global in the main Node.js process. Because that global is used on the request-authentication path, the instance then fails every authenticated request, causing an instance-wide denial of service for all users until the process is restarted.</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/n8n-io/n8n/security/advisories/GHSA-xwx6-jjhv-84p8</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>NVD</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>npm</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>20260901225433</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>CVE-2026-72763</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>n8n</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>n8n</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1.123.67|&gt;=2.31.0,&lt;2.31.5|==2.32.0</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>CVSS:3.1/AV:N/AC:L/PR:L/UI:N/S:U/C:H/I:N/A:N</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>20260811</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>20260901</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>n8n before 1.123.67, 2.31.5, and 2.32.1 validates credential-access only for a node's top-level credentials and not for credentials referenced inside an Execute Sub-workflow node's inline workflow JSON. A member with Editor access to a shared workflow (when workflow sharing is enabled) who knows a target credential's ID can reference that credential in the inline JSON; it passes save-time and runtime validation and resolves in the parent workflow's project context, allowing the attacker to use or exfiltrate credentials they are not permitted to access.</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/n8n-io/n8n/security/advisories/GHSA-cj9h-qx8g-pq2g</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>NVD</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>npm</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>20260901225433</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>CVE-2026-72770</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>n8n</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>n8n</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1.123.67|&gt;=2.31.0,&lt;2.31.5|&gt;=2.32.0,&lt;2.32.1</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>CVSS:3.1/AV:N/AC:L/PR:L/UI:N/S:U/C:H/I:N/A:N</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>20260811</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>20260901</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>n8n versions before 1.123.67 contain a path traversal vulnerability in the Git node's fetch, pull, and push-tags operations that allows authenticated users to bypass repository-path containment checks. Attackers with workflow create/execute rights can point allowlisted remote configurations at local paths outside the sandbox to pull arbitrary git repositories and read their files and history.</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/n8n-io/n8n/security/advisories/GHSA-gf29-4f56-r2jf</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>NVD</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>npm</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>20260901225433</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>CVE-2026-77074</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>n8n</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>n8n</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1.123.69|&gt;=2.33.0,&lt;2.33.4|==2.34.0</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>CVSS:3.1/AV:N/AC:L/PR:L/UI:N/S:U/C:H/I:N/A:N</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>20260820</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>20260901</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>1.123.69 이전의 n8n 버전에는 인증된 사용자가 MVG 프리미티브를 삽입할 수 있도록 허용하는 이미지 편집 노드의 텍스트 그리기 작업에 서버측 요청 위조 취약점이 포함되어 있습니다. 공격자는 악의적인 텍스트 값을 조작하여 임의의 주소에 대한 블라인드 아웃바운드 HTTP 요청을 발행하거나 로컬 파일에 액세스할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/n8n-io/n8n/security/advisories/GHSA-233r-fpgw-fx8x</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>NVD</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>npm</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>20260901225433</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>CVE-2026-77076</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>n8n</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>n8n</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1.123.69|&gt;=2.33.0,&lt;2.33.4|==2.34.0</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>CVSS:3.1/AV:N/AC:L/PR:L/UI:N/S:U/C:H/I:N/A:N</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>20260820</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>20260901</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>1.123.69, 2.33.4 및 2.34.1 이전의 n8n 버전에는 GraphQL 노드에 정보 공개 취약성이 포함되어 있습니다. GraphQL 요청이 연결 수준에서 실패하면 노드는 n8n의 표준 오류 유형으로 래핑하는 대신 기본 HTTP 클라이언트 오류를 ​​변경하지 않고 다시 발생시킵니다. 해당 오류에는 실행 엔진이 그대로 유지하는 해독된 자격 증명 비밀을 포함하여 라이브 요청의 헤더가 포함되어 있습니다. 결과 실행을 읽을 수 있는 인증된 사용자는 저장된 실행 데이터에서 해독된 자격 증명 비밀을 검색할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/n8n-io/n8n/security/advisories/GHSA-9fqj-7wc5-cwhx</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>NVD</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>npm</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>20260901225433</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>CVE-2026-77085</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>n8n</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>n8n</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>&gt;=2.33.0,&lt;2.33.4|==2.34.0</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>2.33.4</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>CVSS:3.1/AV:N/AC:L/PR:L/UI:N/S:U/C:H/I:N/A:N</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>20260820</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>20260901</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>2.34.1 이전의 n8n 및 2.33.4 이전의 2.33.x에는 SearXNG 에이전트 도구에 SSRF 보호 우회 기능이 포함되어 있습니다. 이 도구는 n8n의 중앙 집중식 SSRF 보호를 통해 라우팅되지 않은 원시 HTTP 클라이언트를 사용하여 사용자 제공 API URL에 요청을 보냈습니다. N8N_SSRF_PROTECTION_ENABLED=true인 인스턴스에서 SearXNG 자격 증명을 생성하고 개인 에이전트를 구성할 수 있는 권한이 있는 인증된 사용자는 API URL을 내부 호스트로 설정하여 n8n 서버가 해당 호스트에 연결하고 에이전트 채팅 출력을 통해 응답 콘텐츠를 반환하도록 할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/n8n-io/n8n/security/advisories/GHSA-9rp2-wm75-c5fj</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>NVD</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>npm</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>20260901225433</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>CVE-2026-84303</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>gRPC</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>gRPC Authors</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1.83.1</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>1.83.1</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>CVSS:4.0/AV:N/AC:L/AT:P/PR:N/UI:N/VC:L/VI:L/VA:N/SC:N/SI:N/SA:N/E:X/CR:X/IR:X/AR:X/MAV:X/MAC:X/MAT:X/MPR:X/MUI:X/MVC:X/MVI:X/MVA:X/MSC:X/MSI:X/MSA:X/S:X/AU:X/R:X/V:X/RE:X/U:X</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>20260901</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>20260901</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>gRPC-Go is the Go language implementation of gRPC. Prior to 1.83.1, the xDS RBAC HTTP filter in internal/xds/httpfilter/rbac/rbac.go does not lowercase header matcher names in normalizeHeaderMatcher even though incoming metadata keys are lowercase. A DENY policy using a mixed-case name such as X-Role or User-Agent therefore does not match and fails open, allowing requests that should be rejected. The same case mismatch permits :Scheme or Grpc-Status to evade gRFC A41 validation and prevents Host from being rewritten to :authority. This issue is fixed in version 1.83.1.</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/grpc/grpc-go/commit/db9482836c298f234c896cf82ab68cafc78237f8</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>NVD</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>pypi</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>20260901225433</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>CVE-2026-78605</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Elasticsearch</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Elastic</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>CVSS:3.1/AV:N/AC:H/PR:N/UI:N/S:U/C:H/I:N/A:N</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>20260901</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>20260901</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>[버전범위 불명확] Inconsistent Interpretation of HTTP Requests ('HTTP Request Smuggling') (CWE-444) in Elasticsearch can lead to information disclosure via HTTP Request Smuggling (CAPEC-33). Under specific proxy deployment configurations, a network attacker could obtain confidential responses intended for other authenticated users.</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>https://discuss.elastic.co/t/elasticsearch-8-19-20-9-4-5-9-5-1-security-update-esa-2026-141/390092</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>NVD</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>pypi</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>20260901225433</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>CVE-2026-77083</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>n8n</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>n8n</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1.123.69|&gt;=2.0.0,&lt;2.33.4|==2.34.0</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>CVSS:3.1/AV:N/AC:H/PR:L/UI:N/S:U/C:H/I:L/A:N</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>20260820</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>20260901</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>n8n은 워크플로우 자동화 플랫폼입니다. 1.123.69, 2.33.4 및 2.34.1 이전 버전에서는 JavaScript Code 노드의 VM 샌드박스가 샌드박스의 Function.prototype을 고정하지 않았으므로 인증된 사용자가 워크플로를 생성 및 실행하여 Code 노드 실행 내에서 이를 오염시키고 호스트의 globalThis에 대한 참조를 복구하여 샌드박스 이스케이프가 발생하도록 허용했습니다. 전체 익스플로잇 체인은 배포 구성에서 허용 목록에 있는 가져오기로 사용 가능한 특정 모듈에 따라 달라집니다. 이 문제는 버전 1.123.69, 2.33.4 및 2.34.1에서 해결되었습니다.</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/n8n-io/n8n/security/advisories/GHSA-c9c6-rq46-h25v</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>NVD</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>npm</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>20260901225433</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>CVE-2026-47630</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Triton Inference Server</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>nvidia</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>&lt;=26.05</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>CVSS:3.1/AV:L/AC:L/PR:L/UI:N/S:U/C:H/I:N/A:N</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>20260818</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>20260901</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>Linux용 NVIDIA Triton 추론 서버에는 공격자가 절대 경로 통과를 유발할 수 있는 취약점이 포함되어 있습니다. 악용이 성공하면 코드가 실행될 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/NVIDIA/product-security/tree/main/2026/5865</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>NVD</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>github</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>20260901225433</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>CVE-2026-78607</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Elasticsearch</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Elastic</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>CVSS:3.1/AV:N/AC:L/PR:L/UI:N/S:U/C:L/I:L/A:N</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>20260901</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>20260901</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>[버전범위 불명확] Missing Authorization (CWE-862) in the Elasticsearch custom inference service can lead to information disclosure via Privilege Abuse (CAPEC-122). A user holding only inference execution privileges could cause outbound inference traffic to be directed to a destination of their choosing and could cause administrator-provisioned credentials to be exposed.</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>https://discuss.elastic.co/t/elasticsearch-8-19-19-9-3-8-9-4-4-9-5-1-security-update-esa-2026-143/390094</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>NVD</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>pypi</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>20260901225433</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>CVE-2026-56143</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Elasticsearch</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Elastic</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>4.9</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>CVSS:4.0/AV:N/AC:L/AT:P/PR:L/UI:N/VC:N/VI:N/VA:N/SC:H/SI:N/SA:N/E:X/CR:X/IR:X/AR:X/MAV:X/MAC:X/MAT:X/MPR:X/MUI:X/MVC:X/MVI:X/MVA:X/MSC:X/MSI:X/MSA:X/S:X/AU:X/R:X/V:X/RE:X/U:X</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>20260811</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>20260831</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>n8n before 2.31.5 and 2.32.x before 2.32.1 contain a path-confinement bypass in the @n8n/computer-use file-search (search_files) tool. A crafted search pattern can bypass the base-directory confinement check and expand to locations outside the configured directory, causing the tool to return the names and contents of arbitrary local files readable by the daemon's OS user. Any deployment where an actor can influence the tool's search input is affected.</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>https://github.com/n8n-io/n8n/security/advisories/GHSA-pf2q-pxhf-hgmw</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>CVSS:3.1/AV:N/AC:L/PR:H/UI:N/S:U/C:N/I:N/A:H</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>20260901</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>20260901</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>[버전범위 불명확] Allocation of Resources Without Limits or Throttling (CWE-770) in Elasticsearch can lead to a denial of service via Excessive Allocation (CAPEC-130). A user with elevated privileges can submit a specially crafted request that causes excessive memory consumption, which may render the affected node unavailable.</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>https://discuss.elastic.co/t/elasticsearch-8-19-20-9-3-0-security-update-esa-2026-47/390084</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
         <is>
           <t>NVD</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>pypi</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>20260901225433</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>CVE-2026-72685</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Elasticsearch</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>elastic</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>&gt;=8.0.0,&lt;8.19.20|&gt;=9.0.0,&lt;9.4.5</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr"/>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>CVSS:3.1/AV:N/AC:L/PR:L/UI:N/S:U/C:N/I:N/A:L</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>20260813</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>20260901</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>Elasticsearch의 결함으로 인해 문서를 색인화할 수 있는 권한이 낮은 인증된 사용자가 조작된 사용자 제공 입력이 포함된 작은 문서 하나를 제출할 수 있습니다. 그러한 문서 하나를 처리하면 너무 많은 시간 동안 제한된 풀의 작업자 스레드를 차지하게 되어 영향을 받은 노드에서 인덱싱 작업의 가용성이 저하됩니다.</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>https://discuss.elastic.co/t/elasticsearch-8-19-20-9-4-5-security-update-esa-2026-77/389500</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>NVD</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>pypi</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>20260901225433</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>CVE-2026-77069</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>n8n</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>n8n</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1.123.69|&gt;=2.33.0,&lt;2.33.4|==2.34.0</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>CVSS:3.1/AV:N/AC:L/PR:L/UI:N/S:U/C:L/I:N/A:N</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>20260820</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>20260901</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>n8n before 1.123.69, 2.33.4, and 2.34.1 contains an SSRF protection bypass in the OAuth2 credential authorization-code-to-access-token exchange. While OAuth2 discovery and dynamic-client-registration requests use n8n's SSRF-protected HTTP client, the token exchange uses a separate client with no SSRF guard. A user with credential-creation permissions can set the access-token URL to an internal address and complete the OAuth2 flow, causing n8n to send a fixed-shape token-exchange POST to that target and reflect its response body back to the attacker (limited to what the target returns to this specific request).</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/n8n-io/n8n/security/advisories/GHSA-c4f6-59xq-95ww</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>NVD</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
         <is>
           <t>npm</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>20260901001242</t>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>20260901225433</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>CVE-2026-77073</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>n8n</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>n8n</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>&lt;2.33.4|==2.34.0</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>2.33.4</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>CVSS:3.1/AV:N/AC:L/PR:L/UI:N/S:U/C:N/I:L/A:N</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>20260820</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>20260901</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>2.34.1 이전의 n8n 버전에는 인증 유형이 표현식으로 설정된 경우 MCP create_workflow_from_code 도구의 자격 증명 유효성 검사 우회가 포함되어 있습니다. 유효한 MCP Bearer API 키와 대상 자격 증명 ID에 대한 지식을 갖춘 공격자는 다른 프로젝트의 워크플로에서 무단 프로젝트 간 자격 증명 참조를 유지할 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/n8n-io/n8n/security/advisories/GHSA-vfrj-582q-mvcp</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>NVD</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>npm</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>20260901225433</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>CVE-2026-77082</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>n8n</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>n8n</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>&lt;1.123.69|&gt;=2.0.0,&lt;2.33.4|==2.34.0</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>CVSS:3.1/AV:N/AC:L/PR:L/UI:N/S:U/C:N/I:N/A:L</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>20260820</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>20260901</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>1.123.69 이전의 n8n, 2.33.4 이전의 2.x 및 2.34.1 이전의 2.34.x에는 필터 및 스위치 노드에 정규식 서비스 거부(ReDoS) 취약점이 포함되어 있습니다. 이 취약점은 새로운 RegExp()를 사용하여 사용자 제공 정규식 패턴을 컴파일하고 복잡성 검증이나 실행 시간 초과 없이 작업자 스레드에서 동기식으로 실행합니다. 정교하게 만들어진 정규식 패턴은 처리된 데이터 항목별로 작업자를 장기간 차단하여 동일한 작업자에 대한 다른 워크플로 실행을 지연시킬 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/n8n-io/n8n/security/advisories/GHSA-q3fv-295f-qfpf</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>NVD</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>npm</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>20260901225433</t>
         </is>
       </c>
     </row>
@@ -2058,7 +4602,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>20260901001237</t>
+          <t>20260901225428</t>
         </is>
       </c>
     </row>
@@ -2070,7 +4614,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>20260901001617</t>
+          <t>20260901225929</t>
         </is>
       </c>
     </row>
@@ -2210,7 +4754,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>51</t>
         </is>
       </c>
     </row>
@@ -2222,7 +4766,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -2234,7 +4778,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>39</t>
         </is>
       </c>
     </row>
